--- a/artfynd/A 45717-2021 artfynd.xlsx
+++ b/artfynd/A 45717-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117788381</v>
+        <v>117788199</v>
       </c>
       <c r="B2" t="n">
-        <v>97857</v>
+        <v>90517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372534</v>
+        <v>372602</v>
       </c>
       <c r="R2" t="n">
-        <v>6938682</v>
+        <v>6938636</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117788199</v>
+        <v>117788380</v>
       </c>
       <c r="B3" t="n">
-        <v>90517</v>
+        <v>104914</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372602</v>
+        <v>372534</v>
       </c>
       <c r="R3" t="n">
-        <v>6938636</v>
+        <v>6938682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117788380</v>
+        <v>117788381</v>
       </c>
       <c r="B4" t="n">
-        <v>104914</v>
+        <v>97857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 45717-2021 artfynd.xlsx
+++ b/artfynd/A 45717-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117788199</v>
+        <v>117788381</v>
       </c>
       <c r="B2" t="n">
-        <v>90517</v>
+        <v>97859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>372602</v>
+        <v>372534</v>
       </c>
       <c r="R2" t="n">
-        <v>6938636</v>
+        <v>6938682</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117788380</v>
+        <v>117788199</v>
       </c>
       <c r="B3" t="n">
-        <v>104914</v>
+        <v>90519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372534</v>
+        <v>372602</v>
       </c>
       <c r="R3" t="n">
-        <v>6938682</v>
+        <v>6938636</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117788381</v>
+        <v>117788380</v>
       </c>
       <c r="B4" t="n">
-        <v>97857</v>
+        <v>104916</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 45717-2021 artfynd.xlsx
+++ b/artfynd/A 45717-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>117788380</v>
       </c>
       <c r="B2" t="n">
-        <v>104919</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117788199</v>
+        <v>117788381</v>
       </c>
       <c r="B3" t="n">
-        <v>90521</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372602</v>
+        <v>372534</v>
       </c>
       <c r="R3" t="n">
-        <v>6938636</v>
+        <v>6938682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,108 +866,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>117788381</v>
-      </c>
-      <c r="B4" t="n">
-        <v>97861</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Funäsdalsberget, Hjd</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>372534</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6938682</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Tännäs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2024-06-15</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45717-2021 artfynd.xlsx
+++ b/artfynd/A 45717-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117788380</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117788381</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>